--- a/Unterlagen/Stueckliste_RevE_20261012.xlsx
+++ b/Unterlagen/Stueckliste_RevE_20261012.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_DIM\_GitHubRepository\ChickenGateSystem\Unterlagen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7089FD0-8464-4FB7-B40B-7ABCA5A3103C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{033DF02C-3178-4DBF-819C-828FE551E933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Stückliste" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_A100000">Stückliste!$A$9509</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Stückliste!$A$5:$J$72</definedName>
+    <definedName name="_A100000">Stückliste!$A$9507</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Stückliste!$A$5:$J$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="251">
   <si>
     <t>Art.-Nr.</t>
   </si>
@@ -339,9 +339,6 @@
     <t>Panasonic</t>
   </si>
   <si>
-    <t>Elektrolytkondensator, 100 µF, 50 V, ±20%, Radial, 6000 Stunden/105°C</t>
-  </si>
-  <si>
     <t>MBB02070C2201FCT00</t>
   </si>
   <si>
@@ -384,15 +381,6 @@
     <t>651-1755752</t>
   </si>
   <si>
-    <t>Monostabiles Relais  /  1-polig  /  5VDC</t>
-  </si>
-  <si>
-    <t>Miniatur-Solid-State-Relais, OPT- 5DC/ 24DC/ 2</t>
-  </si>
-  <si>
-    <t>651-2967989</t>
-  </si>
-  <si>
     <t>Diodes Incorporated</t>
   </si>
   <si>
@@ -492,9 +480,6 @@
     <t>576-P6KE18A</t>
   </si>
   <si>
-    <t>667-EEU-FR1H101B</t>
-  </si>
-  <si>
     <t>576-55900000001</t>
   </si>
   <si>
@@ -519,15 +504,6 @@
     <t>80-C320C104K3R5TA</t>
   </si>
   <si>
-    <t>ECA-1EM220I</t>
-  </si>
-  <si>
-    <t>667-ECA-1EM220I</t>
-  </si>
-  <si>
-    <t>Elektrolytkondensator, 22 µF, 25 V, ±20%, Radial, 2000 Stunden/105°C</t>
-  </si>
-  <si>
     <t>637-1N4002</t>
   </si>
   <si>
@@ -549,12 +525,6 @@
     <t>301-39-054</t>
   </si>
   <si>
-    <t>Leistungs-MOSFET, n-Kanal, 30 V, 60 A, 0.0087 ohm, TO-220AB</t>
-  </si>
-  <si>
-    <t>485-355</t>
-  </si>
-  <si>
     <t>Adafruit</t>
   </si>
   <si>
@@ -594,12 +564,6 @@
     <t>80-C315C300F3G5TA</t>
   </si>
   <si>
-    <t xml:space="preserve">  Zenerdiode 5,1V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Zenerdiode 4,7V - Alternative</t>
-  </si>
-  <si>
     <t>BZX55B4V7-TAP</t>
   </si>
   <si>
@@ -609,15 +573,6 @@
     <t>78-BZX55B4V7-TAP</t>
   </si>
   <si>
-    <t>BZX55B5V1-TAP</t>
-  </si>
-  <si>
-    <t>Zener-Diode, 5.1 V, 500 mW, DO-35, ± 2%-Tolerance</t>
-  </si>
-  <si>
-    <t>78-BZX55B5V1-TAP</t>
-  </si>
-  <si>
     <t>Infineon Technologies</t>
   </si>
   <si>
@@ -630,27 +585,9 @@
     <t>942-IRLU024NPBF</t>
   </si>
   <si>
-    <t>355  (identisch zu IRLB8721)</t>
-  </si>
-  <si>
     <t xml:space="preserve">  MOSFET zur Leistungssteuerung</t>
   </si>
   <si>
-    <t xml:space="preserve">  MOSFET zur Leistungssteuerung - Alternative</t>
-  </si>
-  <si>
-    <t>Leistungs-MOSFET, n-Kanal, 55 V, 60 A, 0.0135 ohm, TO-251-3</t>
-  </si>
-  <si>
-    <t>Reichelt</t>
-  </si>
-  <si>
-    <t>IRLU2905ZPBF</t>
-  </si>
-  <si>
-    <t>IRLU 2905Z</t>
-  </si>
-  <si>
     <t>Nextion</t>
   </si>
   <si>
@@ -741,60 +678,9 @@
     <t>594-MBB02070C4702FCT</t>
   </si>
   <si>
-    <t>EEU-FR1H101B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Kondensator 100uF  / 50V  /  12DC-Versorgung - Elko</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Kondensator 470uF  / 25V   /  5V-IC-Versorgung - Elko</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Kondensator 100nF  / 25V  /  5V-IC-Versorgung - Keramik</t>
   </si>
   <si>
-    <t xml:space="preserve">  Kondensator 22uF  / 25V  /  5V-Nextion-Versorgung - Elko</t>
-  </si>
-  <si>
-    <t>EEU-FR1E471L</t>
-  </si>
-  <si>
-    <t>Elektrolytkondensator, 470 µF, 25 V, ±20%, Radial, 9000 Stunden/105°C</t>
-  </si>
-  <si>
-    <t>667-EEU-FR1E471L</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Kondensator 470uF  / 50V  /  12DC-Versorgung - Elko</t>
-  </si>
-  <si>
-    <t>EEU-FR1H471</t>
-  </si>
-  <si>
-    <t>Elektrolytkondensator, 470 µF, 50 V, ±20%, Radial, 10000 Stunden/105°C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">667-EEU-FR1H471 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  TVS-Überspannungsdiode 15,3V - Hauptspeisung</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  TVS-Überspannungsdiode 15,3V - Linearmotor - Bidrektiional</t>
-  </si>
-  <si>
-    <t>P6KE18CA</t>
-  </si>
-  <si>
-    <t>TVS-Diode, P4KE, Biidirektional, 15.3 V, DO-204AC</t>
-  </si>
-  <si>
-    <t>576-P6KE18CA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Schottky-Diode Eingangsseitig für 5VDC-Linearregler</t>
-  </si>
-  <si>
     <t>1N5822</t>
   </si>
   <si>
@@ -805,6 +691,102 @@
   </si>
   <si>
     <t>821-1N5822</t>
+  </si>
+  <si>
+    <t>TSM680P06CH X0G</t>
+  </si>
+  <si>
+    <t>Leistungs-MOSFET, p-Kanal, 60 V, 18 A, 0.054 ohm, TO-251-S3</t>
+  </si>
+  <si>
+    <t>821-TSM680P06CHX0G</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  MOSFET  /  Leistungsschaltung</t>
+  </si>
+  <si>
+    <t>EEU-FR1H221</t>
+  </si>
+  <si>
+    <t>Elektrolytkondensator, 220 µF, 50 V, ±20%, Radial, 8000 Stunden/105°C</t>
+  </si>
+  <si>
+    <t>667-EEU-FR1H221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator 220uF  / 50V  /  12DC Linearregler - Elko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator   10uF  / 50V  /  12DC Linearregler - Keramik</t>
+  </si>
+  <si>
+    <t>TDK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator   22uF  / 25V  /  5VDC Linearregler - Keramik</t>
+  </si>
+  <si>
+    <t>FG22X7R1E226MRT00</t>
+  </si>
+  <si>
+    <t>Keramik-Vielschichtkondensator MLCC – bedrahtet RAD 25V 22uF X7R 20% LS:5mm</t>
+  </si>
+  <si>
+    <t>810-FG22X7R1E226MRT0</t>
+  </si>
+  <si>
+    <t>FG20X7R1H106KRT00</t>
+  </si>
+  <si>
+    <t>Keramik-Vielschichtkondensator MLCC – bedrahtet RAD 50V 10uF X7R 10% LS:5mm</t>
+  </si>
+  <si>
+    <t>810-FG20X7R1H106KRT0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Schottky-Diode für 5VDC-Linearregler</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator   1uF  / 50V  /  Motorentstörung - Keramik</t>
+  </si>
+  <si>
+    <t>FG24X7R1H105KRT00</t>
+  </si>
+  <si>
+    <t>Keramik-Vielschichtkondensator MLCC – bedrahtet RAD 50V 1uF X7R 10% LS:5mm</t>
+  </si>
+  <si>
+    <t>810-FG24X7R1H105KRT0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  TVS-Überspannungsdiode 15,3V - Hauptspeisung &amp; Motor</t>
+  </si>
+  <si>
+    <t>BZX55B12-TAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Zenerdiode 4,7V -  2%-Toleranz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Zenerdiode 12.0V -  2%-Toleranz</t>
+  </si>
+  <si>
+    <t>Zener-Diode, 12 V, 500 mW, DO-35, ± 2%-Tolerance</t>
+  </si>
+  <si>
+    <t>78-BZX55B12-TAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Kondensator 330nF  / 25V  /  5V-HMI-Versorgung - Keramik</t>
+  </si>
+  <si>
+    <t>Keramikkondensator, 0.33 µF, 25 V, ±10%, Radial, X7R, 2.54 mm</t>
+  </si>
+  <si>
+    <t>80-C317C334K3R5TA</t>
+  </si>
+  <si>
+    <t>C317C334K3R5TA</t>
   </si>
 </sst>
 </file>
@@ -1630,7 +1612,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:K72"/>
+  <dimension ref="A2:K70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="14.1" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51.28515625" style="1" customWidth="1"/>
@@ -1754,7 +1736,7 @@
         <v>50</v>
       </c>
       <c r="I9" s="55">
-        <f t="shared" ref="I9:I70" si="0">J9*H9</f>
+        <f t="shared" ref="I9:I68" si="0">J9*H9</f>
         <v>50</v>
       </c>
       <c r="J9" s="8">
@@ -1911,10 +1893,10 @@
         <v>6</v>
       </c>
       <c r="C15" s="32" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D15" s="32" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E15" s="36" t="s">
         <v>98</v>
@@ -1923,7 +1905,7 @@
         <v>53</v>
       </c>
       <c r="G15" s="34" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H15" s="35">
         <v>8.6</v>
@@ -1938,7 +1920,7 @@
     </row>
     <row r="16" spans="1:11" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="B16" s="31" t="s">
         <v>6</v>
@@ -1947,55 +1929,55 @@
         <v>99</v>
       </c>
       <c r="D16" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="E16" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="E16" s="36" t="s">
-        <v>105</v>
-      </c>
-      <c r="F16" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G16" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="H16" s="38">
+      <c r="F16" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="65" t="s">
+        <v>147</v>
+      </c>
+      <c r="H16" s="66">
         <v>0.6</v>
       </c>
-      <c r="I16" s="55">
-        <f t="shared" ref="I16:I17" si="1">J16*H16</f>
-        <v>0.6</v>
+      <c r="I16" s="67">
+        <f t="shared" ref="I16" si="1">J16*H16</f>
+        <v>1.7999999999999998</v>
       </c>
       <c r="J16" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="17" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="B17" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C17" s="32" t="s">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="D17" s="32" t="s">
-        <v>249</v>
+        <v>215</v>
       </c>
       <c r="E17" s="63" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="F17" s="64" t="s">
         <v>53</v>
       </c>
       <c r="G17" s="65" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="H17" s="66">
         <v>0.6</v>
       </c>
-      <c r="I17" s="55">
-        <f t="shared" si="1"/>
+      <c r="I17" s="67">
+        <f t="shared" si="0"/>
         <v>0.6</v>
       </c>
       <c r="J17" s="10">
@@ -2004,32 +1986,32 @@
     </row>
     <row r="18" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="17" t="s">
-        <v>252</v>
+        <v>226</v>
       </c>
       <c r="B18" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C18" s="32" t="s">
-        <v>254</v>
+        <v>100</v>
       </c>
       <c r="D18" s="32" t="s">
-        <v>253</v>
+        <v>223</v>
       </c>
       <c r="E18" s="63" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="F18" s="64" t="s">
         <v>53</v>
       </c>
       <c r="G18" s="65" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="H18" s="66">
-        <v>0.6</v>
-      </c>
-      <c r="I18" s="55">
-        <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>1.2</v>
+      </c>
+      <c r="I18" s="67">
+        <f t="shared" si="0"/>
+        <v>1.2</v>
       </c>
       <c r="J18" s="10">
         <v>1</v>
@@ -2037,65 +2019,65 @@
     </row>
     <row r="19" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
-        <v>243</v>
+        <v>227</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C19" s="32" t="s">
-        <v>100</v>
+        <v>228</v>
       </c>
       <c r="D19" s="32" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="E19" s="63" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="F19" s="64" t="s">
         <v>53</v>
       </c>
       <c r="G19" s="65" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="H19" s="66">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="I19" s="67">
-        <f t="shared" si="0"/>
-        <v>1.2</v>
+        <f>J19*H19</f>
+        <v>0.4</v>
       </c>
       <c r="J19" s="10">
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="60" t="s">
-        <v>236</v>
-      </c>
-      <c r="B20" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C20" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="D20" s="50" t="s">
-        <v>235</v>
-      </c>
-      <c r="E20" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G20" s="58" t="s">
-        <v>152</v>
-      </c>
-      <c r="H20" s="53">
-        <v>0.6</v>
-      </c>
-      <c r="I20" s="54">
-        <f t="shared" ref="I20" si="2">J20*H20</f>
-        <v>0.6</v>
+      <c r="A20" s="17" t="s">
+        <v>229</v>
+      </c>
+      <c r="B20" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="E20" s="63" t="s">
+        <v>231</v>
+      </c>
+      <c r="F20" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G20" s="65" t="s">
+        <v>232</v>
+      </c>
+      <c r="H20" s="66">
+        <v>0.4</v>
+      </c>
+      <c r="I20" s="67">
+        <f>J20*H20</f>
+        <v>0.4</v>
       </c>
       <c r="J20" s="10">
         <v>1</v>
@@ -2103,65 +2085,65 @@
     </row>
     <row r="21" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="17" t="s">
-        <v>237</v>
+        <v>214</v>
       </c>
       <c r="B21" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C21" s="32" t="s">
-        <v>100</v>
+        <v>39</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="E21" s="63" t="s">
-        <v>241</v>
-      </c>
-      <c r="F21" s="64" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="65" t="s">
-        <v>242</v>
-      </c>
-      <c r="H21" s="66">
-        <v>0.8</v>
-      </c>
-      <c r="I21" s="67">
-        <f t="shared" si="0"/>
-        <v>0.8</v>
+        <v>154</v>
+      </c>
+      <c r="E21" s="36" t="s">
+        <v>153</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="39" t="s">
+        <v>155</v>
+      </c>
+      <c r="H21" s="38">
+        <v>0.4</v>
+      </c>
+      <c r="I21" s="55">
+        <f>J21*H21</f>
+        <v>2.4000000000000004</v>
       </c>
       <c r="J21" s="10">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="60" t="s">
-        <v>239</v>
-      </c>
-      <c r="B22" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="50" t="s">
-        <v>100</v>
-      </c>
-      <c r="D22" s="50" t="s">
-        <v>161</v>
-      </c>
-      <c r="E22" s="51" t="s">
-        <v>163</v>
-      </c>
-      <c r="F22" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G22" s="58" t="s">
-        <v>162</v>
-      </c>
-      <c r="H22" s="53">
-        <v>0.2</v>
-      </c>
-      <c r="I22" s="54">
+      <c r="A22" s="17" t="s">
+        <v>247</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="E22" s="63" t="s">
+        <v>248</v>
+      </c>
+      <c r="F22" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="65" t="s">
+        <v>249</v>
+      </c>
+      <c r="H22" s="66">
+        <v>0.4</v>
+      </c>
+      <c r="I22" s="67">
         <f>J22*H22</f>
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="J22" s="10">
         <v>1</v>
@@ -2169,35 +2151,35 @@
     </row>
     <row r="23" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="17" t="s">
+        <v>237</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="D23" s="32" t="s">
         <v>238</v>
       </c>
-      <c r="B23" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C23" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>158</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>160</v>
-      </c>
-      <c r="H23" s="38">
+      <c r="E23" s="63" t="s">
+        <v>239</v>
+      </c>
+      <c r="F23" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G23" s="65" t="s">
+        <v>240</v>
+      </c>
+      <c r="H23" s="66">
         <v>0.4</v>
       </c>
-      <c r="I23" s="55">
+      <c r="I23" s="67">
         <f>J23*H23</f>
-        <v>2.4000000000000004</v>
+        <v>0.4</v>
       </c>
       <c r="J23" s="10">
-        <v>6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
@@ -2212,13 +2194,13 @@
         <v>55900000001</v>
       </c>
       <c r="E24" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F24" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G24" s="34" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="H24" s="35">
         <v>1</v>
@@ -2233,7 +2215,7 @@
     </row>
     <row r="25" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B25" s="31"/>
       <c r="C25" s="32" t="s">
@@ -2243,7 +2225,7 @@
         <v>37212000411</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" s="32" t="s">
         <v>34</v>
@@ -2274,7 +2256,7 @@
         <v>37005000430</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F26" s="32" t="s">
         <v>34</v>
@@ -2295,23 +2277,23 @@
     </row>
     <row r="27" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="17" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B27" s="31"/>
       <c r="C27" s="32" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D27" s="32" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F27" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G27" s="34" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="H27" s="35">
         <v>0.4</v>
@@ -2326,29 +2308,29 @@
     </row>
     <row r="28" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="17" t="s">
-        <v>209</v>
+        <v>188</v>
       </c>
       <c r="B28" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="32" t="s">
-        <v>205</v>
+        <v>184</v>
       </c>
       <c r="D28" s="32" t="s">
-        <v>206</v>
+        <v>185</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="F28" s="32" t="s">
-        <v>208</v>
+        <v>187</v>
       </c>
       <c r="G28" s="37"/>
       <c r="H28" s="38">
         <v>29</v>
       </c>
       <c r="I28" s="55">
-        <f t="shared" ref="I28" si="3">J28*H28</f>
+        <f t="shared" ref="I28" si="2">J28*H28</f>
         <v>29</v>
       </c>
       <c r="J28" s="10">
@@ -2447,7 +2429,7 @@
         <v>0.7</v>
       </c>
       <c r="I31" s="54">
-        <f t="shared" ref="I31" si="4">J31*H31</f>
+        <f t="shared" ref="I31" si="3">J31*H31</f>
         <v>0</v>
       </c>
       <c r="J31" s="10">
@@ -2465,16 +2447,16 @@
         <v>33</v>
       </c>
       <c r="D32" s="32" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="E32" s="63" t="s">
-        <v>222</v>
+        <v>201</v>
       </c>
       <c r="F32" s="64" t="s">
         <v>53</v>
       </c>
       <c r="G32" s="65" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="H32" s="66">
         <v>1.4</v>
@@ -2513,7 +2495,7 @@
         <v>0.35</v>
       </c>
       <c r="I33" s="54">
-        <f t="shared" ref="I33" si="5">J33*H33</f>
+        <f t="shared" ref="I33" si="4">J33*H33</f>
         <v>0</v>
       </c>
       <c r="J33" s="10">
@@ -2528,19 +2510,19 @@
         <v>6</v>
       </c>
       <c r="C34" s="32" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D34" s="32" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F34" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="H34" s="38">
         <v>0.35</v>
@@ -2555,7 +2537,7 @@
     </row>
     <row r="35" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="B35" s="31" t="s">
         <v>6</v>
@@ -2564,16 +2546,16 @@
         <v>39</v>
       </c>
       <c r="D35" s="32" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="F35" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G35" s="39" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="H35" s="38">
         <v>1.1000000000000001</v>
@@ -2588,7 +2570,7 @@
     </row>
     <row r="36" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="17" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B36" s="31" t="s">
         <v>6</v>
@@ -2597,22 +2579,22 @@
         <v>42</v>
       </c>
       <c r="D36" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E36" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="E36" s="36" t="s">
-        <v>134</v>
-      </c>
       <c r="F36" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G36" s="39" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="H36" s="38">
         <v>0.1</v>
       </c>
       <c r="I36" s="55">
-        <f t="shared" ref="I36:I37" si="6">J36*H36</f>
+        <f t="shared" ref="I36:I37" si="5">J36*H36</f>
         <v>0.4</v>
       </c>
       <c r="J36" s="10">
@@ -2621,7 +2603,7 @@
     </row>
     <row r="37" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="17" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="B37" s="31" t="s">
         <v>6</v>
@@ -2630,22 +2612,22 @@
         <v>42</v>
       </c>
       <c r="D37" s="32" t="s">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="E37" s="63" t="s">
-        <v>224</v>
+        <v>203</v>
       </c>
       <c r="F37" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G37" s="39" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="H37" s="38">
         <v>0.2</v>
       </c>
       <c r="I37" s="55">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.4</v>
       </c>
       <c r="J37" s="10">
@@ -2654,7 +2636,7 @@
     </row>
     <row r="38" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B38" s="31" t="s">
         <v>6</v>
@@ -2663,16 +2645,16 @@
         <v>42</v>
       </c>
       <c r="D38" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E38" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="E38" s="63" t="s">
-        <v>135</v>
-      </c>
       <c r="F38" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G38" s="39" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H38" s="38">
         <v>0.1</v>
@@ -2687,7 +2669,7 @@
     </row>
     <row r="39" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="17" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B39" s="31" t="s">
         <v>6</v>
@@ -2696,16 +2678,16 @@
         <v>42</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="F39" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G39" s="39" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="H39" s="38">
         <v>0.1</v>
@@ -2720,7 +2702,7 @@
     </row>
     <row r="40" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="17" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B40" s="31" t="s">
         <v>6</v>
@@ -2729,22 +2711,22 @@
         <v>42</v>
       </c>
       <c r="D40" s="32" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F40" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G40" s="39" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="H40" s="38">
         <v>0.1</v>
       </c>
       <c r="I40" s="55">
-        <f t="shared" ref="I40" si="7">J40*H40</f>
+        <f t="shared" ref="I40" si="6">J40*H40</f>
         <v>0.60000000000000009</v>
       </c>
       <c r="J40" s="10">
@@ -2753,7 +2735,7 @@
     </row>
     <row r="41" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="17" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="B41" s="31" t="s">
         <v>6</v>
@@ -2762,16 +2744,16 @@
         <v>42</v>
       </c>
       <c r="D41" s="32" t="s">
-        <v>227</v>
+        <v>206</v>
       </c>
       <c r="E41" s="36" t="s">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="F41" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G41" s="39" t="s">
-        <v>228</v>
+        <v>207</v>
       </c>
       <c r="H41" s="38">
         <v>0.1</v>
@@ -2786,7 +2768,7 @@
     </row>
     <row r="42" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B42" s="31" t="s">
         <v>6</v>
@@ -2798,13 +2780,13 @@
         <v>50</v>
       </c>
       <c r="E42" s="63" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="F42" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="H42" s="38">
         <v>0.1</v>
@@ -2819,7 +2801,7 @@
     </row>
     <row r="43" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="17" t="s">
-        <v>232</v>
+        <v>211</v>
       </c>
       <c r="B43" s="31" t="s">
         <v>6</v>
@@ -2828,22 +2810,22 @@
         <v>42</v>
       </c>
       <c r="D43" s="32" t="s">
-        <v>231</v>
+        <v>210</v>
       </c>
       <c r="E43" s="63" t="s">
-        <v>233</v>
+        <v>212</v>
       </c>
       <c r="F43" s="64" t="s">
         <v>53</v>
       </c>
       <c r="G43" s="65" t="s">
-        <v>234</v>
+        <v>213</v>
       </c>
       <c r="H43" s="66">
         <v>0.1</v>
       </c>
       <c r="I43" s="67">
-        <f t="shared" ref="I43" si="8">J43*H43</f>
+        <f t="shared" ref="I43" si="7">J43*H43</f>
         <v>0.1</v>
       </c>
       <c r="J43" s="10">
@@ -2852,7 +2834,7 @@
     </row>
     <row r="44" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="17" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B44" s="31" t="s">
         <v>6</v>
@@ -2861,16 +2843,16 @@
         <v>42</v>
       </c>
       <c r="D44" s="32" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E44" s="36" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="F44" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="H44" s="38">
         <v>0.1</v>
@@ -2885,7 +2867,7 @@
     </row>
     <row r="45" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="17" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B45" s="31" t="s">
         <v>6</v>
@@ -2894,16 +2876,16 @@
         <v>42</v>
       </c>
       <c r="D45" s="32" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="E45" s="36" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F45" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G45" s="39" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="H45" s="38">
         <v>0.1</v>
@@ -2918,31 +2900,31 @@
     </row>
     <row r="46" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="23" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="B46" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C46" s="32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D46" s="32" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="F46" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="H46" s="38">
         <v>0.5</v>
       </c>
       <c r="I46" s="55">
-        <f t="shared" ref="I46" si="9">J46*H46</f>
+        <f t="shared" ref="I46" si="8">J46*H46</f>
         <v>3</v>
       </c>
       <c r="J46" s="10">
@@ -2950,65 +2932,65 @@
       </c>
     </row>
     <row r="47" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="59" t="s">
-        <v>186</v>
-      </c>
-      <c r="B47" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C47" s="50" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" s="50" t="s">
-        <v>191</v>
-      </c>
-      <c r="E47" s="51" t="s">
-        <v>192</v>
-      </c>
-      <c r="F47" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G47" s="58" t="s">
-        <v>193</v>
-      </c>
-      <c r="H47" s="53">
+      <c r="A47" s="23" t="s">
+        <v>244</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C47" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="D47" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="E47" s="63" t="s">
+        <v>245</v>
+      </c>
+      <c r="F47" s="64" t="s">
+        <v>53</v>
+      </c>
+      <c r="G47" s="65" t="s">
+        <v>246</v>
+      </c>
+      <c r="H47" s="66">
         <v>0.5</v>
       </c>
-      <c r="I47" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="I47" s="67">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
       </c>
       <c r="J47" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="23" t="s">
-        <v>214</v>
+        <v>193</v>
       </c>
       <c r="B48" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C48" s="32" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D48" s="32" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>213</v>
+        <v>192</v>
       </c>
       <c r="F48" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H48" s="38">
         <v>0.1</v>
       </c>
       <c r="I48" s="55">
-        <f t="shared" ref="I48:I49" si="10">J48*H48</f>
+        <f t="shared" ref="I48:I49" si="9">J48*H48</f>
         <v>0.2</v>
       </c>
       <c r="J48" s="10">
@@ -3017,31 +2999,31 @@
     </row>
     <row r="49" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="23" t="s">
-        <v>215</v>
+        <v>194</v>
       </c>
       <c r="B49" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C49" s="32" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D49" s="32" t="s">
-        <v>210</v>
+        <v>189</v>
       </c>
       <c r="E49" s="36" t="s">
-        <v>212</v>
+        <v>191</v>
       </c>
       <c r="F49" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G49" s="39" t="s">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="H49" s="38">
         <v>0.1</v>
       </c>
       <c r="I49" s="55">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>0.4</v>
       </c>
       <c r="J49" s="10">
@@ -3083,31 +3065,31 @@
     </row>
     <row r="51" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="59" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="B51" s="48" t="s">
         <v>6</v>
       </c>
       <c r="C51" s="50" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D51" s="50">
         <v>161</v>
       </c>
       <c r="E51" s="51" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F51" s="50" t="s">
         <v>1</v>
       </c>
       <c r="G51" s="56" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H51" s="53">
         <v>1.2</v>
       </c>
       <c r="I51" s="54">
-        <f t="shared" ref="I51" si="11">J51*H51</f>
+        <f t="shared" ref="I51" si="10">J51*H51</f>
         <v>0</v>
       </c>
       <c r="J51" s="10">
@@ -3116,25 +3098,25 @@
     </row>
     <row r="52" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="23" t="s">
-        <v>216</v>
+        <v>195</v>
       </c>
       <c r="B52" s="31" t="s">
         <v>6</v>
       </c>
       <c r="C52" s="32" t="s">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="D52" s="32" t="s">
-        <v>218</v>
+        <v>197</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="F52" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G52" s="34" t="s">
-        <v>219</v>
+        <v>198</v>
       </c>
       <c r="H52" s="38">
         <v>1.2</v>
@@ -3149,29 +3131,29 @@
     </row>
     <row r="53" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="23" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B53" s="31"/>
       <c r="C53" s="32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D53" s="32" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F53" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G53" s="34" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H53" s="38">
         <v>1</v>
       </c>
       <c r="I53" s="55">
-        <f t="shared" ref="I53:I55" si="12">J53*H53</f>
+        <f t="shared" ref="I53:I54" si="11">J53*H53</f>
         <v>2</v>
       </c>
       <c r="J53" s="10">
@@ -3179,61 +3161,61 @@
       </c>
     </row>
     <row r="54" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="59" t="s">
-        <v>200</v>
-      </c>
-      <c r="B54" s="48"/>
-      <c r="C54" s="50" t="s">
-        <v>194</v>
-      </c>
-      <c r="D54" s="50" t="s">
-        <v>203</v>
-      </c>
-      <c r="E54" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="F54" s="50" t="s">
-        <v>202</v>
-      </c>
-      <c r="G54" s="56" t="s">
-        <v>204</v>
-      </c>
-      <c r="H54" s="53">
-        <v>1</v>
-      </c>
-      <c r="I54" s="54">
-        <f t="shared" si="12"/>
-        <v>0</v>
+      <c r="A54" s="23" t="s">
+        <v>183</v>
+      </c>
+      <c r="B54" s="31"/>
+      <c r="C54" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="F54" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G54" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="H54" s="38">
+        <v>1.5</v>
+      </c>
+      <c r="I54" s="55">
+        <f t="shared" si="11"/>
+        <v>3</v>
       </c>
       <c r="J54" s="10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="23" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="B55" s="31"/>
       <c r="C55" s="32" t="s">
-        <v>194</v>
+        <v>216</v>
       </c>
       <c r="D55" s="32" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F55" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G55" s="34" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="H55" s="38">
         <v>1.5</v>
       </c>
       <c r="I55" s="55">
-        <f t="shared" si="12"/>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="J55" s="10">
@@ -3241,167 +3223,171 @@
       </c>
     </row>
     <row r="56" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="59" t="s">
-        <v>200</v>
-      </c>
-      <c r="B56" s="48"/>
-      <c r="C56" s="50" t="s">
-        <v>173</v>
-      </c>
-      <c r="D56" s="50" t="s">
-        <v>198</v>
-      </c>
-      <c r="E56" s="51" t="s">
-        <v>171</v>
-      </c>
-      <c r="F56" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G56" s="56" t="s">
-        <v>172</v>
-      </c>
-      <c r="H56" s="53">
-        <v>1.8</v>
-      </c>
-      <c r="I56" s="54">
-        <f t="shared" si="0"/>
-        <v>0</v>
+      <c r="A56" s="23" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="31"/>
+      <c r="C56" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="E56" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="F56" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G56" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="H56" s="38">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="I56" s="55">
+        <f>J56*H56</f>
+        <v>8.6999999999999993</v>
       </c>
       <c r="J56" s="10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B57" s="31"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>6</v>
+      </c>
       <c r="C57" s="40" t="s">
         <v>7</v>
       </c>
       <c r="D57" s="32">
-        <v>2967989</v>
+        <v>1755736</v>
       </c>
       <c r="E57" s="36" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="F57" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="G57" s="34" t="s">
-        <v>118</v>
+      <c r="G57" s="37" t="s">
+        <v>112</v>
       </c>
       <c r="H57" s="38">
-        <v>38.6</v>
+        <v>0.5</v>
       </c>
       <c r="I57" s="55">
         <f t="shared" si="0"/>
-        <v>38.6</v>
+        <v>1</v>
       </c>
       <c r="J57" s="10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="B58" s="31"/>
-      <c r="C58" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D58" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>86</v>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C58" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D58" s="32">
+        <v>1754568</v>
+      </c>
+      <c r="E58" s="63" t="s">
+        <v>96</v>
       </c>
       <c r="F58" s="32" t="s">
         <v>53</v>
       </c>
-      <c r="G58" s="34" t="s">
-        <v>84</v>
+      <c r="G58" s="37" t="s">
+        <v>113</v>
       </c>
       <c r="H58" s="38">
-        <v>8.6999999999999993</v>
+        <v>2.1</v>
       </c>
       <c r="I58" s="55">
-        <f>J58*H58</f>
-        <v>8.6999999999999993</v>
+        <f t="shared" si="0"/>
+        <v>4.2</v>
       </c>
       <c r="J58" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="B59" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C59" s="40" t="s">
+      <c r="A59" s="60" t="s">
+        <v>91</v>
+      </c>
+      <c r="B59" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D59" s="32">
-        <v>1755736</v>
-      </c>
-      <c r="E59" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="F59" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G59" s="37" t="s">
-        <v>113</v>
-      </c>
-      <c r="H59" s="38">
-        <v>0.5</v>
-      </c>
-      <c r="I59" s="55">
-        <f t="shared" si="0"/>
-        <v>1</v>
+      <c r="D59" s="50">
+        <v>1755752</v>
+      </c>
+      <c r="E59" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="F59" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G59" s="52" t="s">
+        <v>114</v>
+      </c>
+      <c r="H59" s="53">
+        <v>1.4</v>
+      </c>
+      <c r="I59" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="J59" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B60" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C60" s="40" t="s">
+      <c r="A60" s="60" t="s">
+        <v>92</v>
+      </c>
+      <c r="B60" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="C60" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="D60" s="32">
-        <v>1754568</v>
-      </c>
-      <c r="E60" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="F60" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G60" s="37" t="s">
-        <v>114</v>
-      </c>
-      <c r="H60" s="38">
-        <v>2.1</v>
-      </c>
-      <c r="I60" s="55">
-        <f t="shared" si="0"/>
+      <c r="D60" s="50">
+        <v>1754584</v>
+      </c>
+      <c r="E60" s="51" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="G60" s="52" t="s">
+        <v>111</v>
+      </c>
+      <c r="H60" s="53">
         <v>4.2</v>
       </c>
+      <c r="I60" s="54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
       <c r="J60" s="10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="60" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="B61" s="48" t="s">
         <v>6</v>
@@ -3410,21 +3396,21 @@
         <v>7</v>
       </c>
       <c r="D61" s="50">
-        <v>1755752</v>
+        <v>1803426</v>
       </c>
       <c r="E61" s="51" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="F61" s="50" t="s">
         <v>53</v>
       </c>
       <c r="G61" s="52" t="s">
-        <v>115</v>
-      </c>
-      <c r="H61" s="53">
-        <v>1.4</v>
-      </c>
-      <c r="I61" s="54">
+        <v>54</v>
+      </c>
+      <c r="H61" s="38">
+        <v>0.6</v>
+      </c>
+      <c r="I61" s="55">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3434,7 +3420,7 @@
     </row>
     <row r="62" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="60" t="s">
-        <v>92</v>
+        <v>56</v>
       </c>
       <c r="B62" s="48" t="s">
         <v>6</v>
@@ -3443,21 +3429,21 @@
         <v>7</v>
       </c>
       <c r="D62" s="50">
-        <v>1754584</v>
+        <v>1745894</v>
       </c>
       <c r="E62" s="51" t="s">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="F62" s="50" t="s">
         <v>53</v>
       </c>
       <c r="G62" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="H62" s="53">
-        <v>4.2</v>
-      </c>
-      <c r="I62" s="54">
+        <v>57</v>
+      </c>
+      <c r="H62" s="38">
+        <v>1.7</v>
+      </c>
+      <c r="I62" s="55">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3466,69 +3452,69 @@
       </c>
     </row>
     <row r="63" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="60" t="s">
-        <v>52</v>
-      </c>
-      <c r="B63" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="49" t="s">
+      <c r="A63" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C63" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D63" s="50">
-        <v>1803426</v>
-      </c>
-      <c r="E63" s="51" t="s">
-        <v>55</v>
-      </c>
-      <c r="F63" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G63" s="52" t="s">
-        <v>54</v>
+      <c r="D63" s="32">
+        <v>1803439</v>
+      </c>
+      <c r="E63" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="F63" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G63" s="37" t="s">
+        <v>167</v>
       </c>
       <c r="H63" s="38">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I63" s="55">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J63" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="60" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" s="48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C64" s="49" t="s">
+      <c r="A64" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B64" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="C64" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="D64" s="50">
-        <v>1745894</v>
-      </c>
-      <c r="E64" s="51" t="s">
-        <v>58</v>
-      </c>
-      <c r="F64" s="50" t="s">
-        <v>53</v>
-      </c>
-      <c r="G64" s="52" t="s">
-        <v>57</v>
+      <c r="D64" s="32">
+        <v>1745904</v>
+      </c>
+      <c r="E64" s="36" t="s">
+        <v>165</v>
+      </c>
+      <c r="F64" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="G64" s="37" t="s">
+        <v>166</v>
       </c>
       <c r="H64" s="38">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="I64" s="55">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="J64" s="10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3542,26 +3528,26 @@
         <v>7</v>
       </c>
       <c r="D65" s="32">
-        <v>1803439</v>
+        <v>1803442</v>
       </c>
       <c r="E65" s="36" t="s">
-        <v>174</v>
+        <v>62</v>
       </c>
       <c r="F65" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G65" s="37" t="s">
-        <v>177</v>
+        <v>61</v>
       </c>
       <c r="H65" s="38">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="I65" s="55">
         <f t="shared" si="0"/>
-        <v>0.9</v>
+        <v>3.5999999999999996</v>
       </c>
       <c r="J65" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3575,31 +3561,31 @@
         <v>7</v>
       </c>
       <c r="D66" s="32">
-        <v>1745904</v>
+        <v>1745917</v>
       </c>
       <c r="E66" s="36" t="s">
-        <v>175</v>
+        <v>63</v>
       </c>
       <c r="F66" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G66" s="37" t="s">
-        <v>176</v>
+        <v>64</v>
       </c>
       <c r="H66" s="38">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="I66" s="55">
         <f t="shared" si="0"/>
-        <v>2.5</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="J66" s="10">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="17" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="B67" s="31" t="s">
         <v>6</v>
@@ -3608,23 +3594,23 @@
         <v>7</v>
       </c>
       <c r="D67" s="32">
-        <v>1803442</v>
-      </c>
-      <c r="E67" s="36" t="s">
-        <v>62</v>
+        <v>1803468</v>
+      </c>
+      <c r="E67" s="63" t="s">
+        <v>67</v>
       </c>
       <c r="F67" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G67" s="37" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="H67" s="38">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="I67" s="55">
         <f t="shared" si="0"/>
-        <v>3.5999999999999996</v>
+        <v>5.4</v>
       </c>
       <c r="J67" s="10">
         <v>3</v>
@@ -3632,7 +3618,7 @@
     </row>
     <row r="68" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="17" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="B68" s="31" t="s">
         <v>6</v>
@@ -3641,121 +3627,55 @@
         <v>7</v>
       </c>
       <c r="D68" s="32">
-        <v>1745917</v>
-      </c>
-      <c r="E68" s="36" t="s">
-        <v>63</v>
+        <v>1748011</v>
+      </c>
+      <c r="E68" s="63" t="s">
+        <v>68</v>
       </c>
       <c r="F68" s="32" t="s">
         <v>53</v>
       </c>
       <c r="G68" s="37" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="H68" s="38">
-        <v>3.4</v>
+        <v>5.5</v>
       </c>
       <c r="I68" s="55">
         <f t="shared" si="0"/>
-        <v>10.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="J68" s="10">
         <v>3</v>
       </c>
     </row>
-    <row r="69" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="B69" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C69" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D69" s="32">
-        <v>1803468</v>
-      </c>
-      <c r="E69" s="63" t="s">
-        <v>67</v>
-      </c>
-      <c r="F69" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G69" s="37" t="s">
-        <v>70</v>
-      </c>
-      <c r="H69" s="38">
-        <v>1.8</v>
-      </c>
-      <c r="I69" s="55">
-        <f t="shared" si="0"/>
-        <v>5.4</v>
-      </c>
-      <c r="J69" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="70" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="D70" s="32">
-        <v>1748011</v>
-      </c>
-      <c r="E70" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="F70" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="G70" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="H70" s="38">
-        <v>5.5</v>
-      </c>
-      <c r="I70" s="55">
-        <f t="shared" si="0"/>
-        <v>16.5</v>
-      </c>
-      <c r="J70" s="10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="27"/>
-      <c r="B71" s="28"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="25"/>
-      <c r="I71" s="25">
-        <f>SUM(I9:I70)</f>
-        <v>238.89999999999989</v>
-      </c>
-      <c r="J71" s="26" t="s">
+    <row r="69" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="27"/>
+      <c r="B69" s="28"/>
+      <c r="G69" s="29"/>
+      <c r="H69" s="25"/>
+      <c r="I69" s="25">
+        <f>SUM(I9:I68)</f>
+        <v>204.39999999999995</v>
+      </c>
+      <c r="J69" s="26" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="6"/>
-      <c r="B72" s="7"/>
-      <c r="C72" s="7"/>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="7"/>
-      <c r="G72" s="7"/>
-      <c r="H72" s="22"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="18"/>
+    <row r="70" spans="1:10" ht="14.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="6"/>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
+      <c r="H70" s="22"/>
+      <c r="I70" s="22"/>
+      <c r="J70" s="18"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:J72" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A5:J70" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <mergeCells count="12">
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A5:A6"/>
@@ -3771,7 +3691,7 @@
     <mergeCell ref="F5:F6"/>
   </mergeCells>
   <phoneticPr fontId="0" type="noConversion"/>
-  <conditionalFormatting sqref="J9:J70">
+  <conditionalFormatting sqref="J9:J68">
     <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
       <formula>0</formula>
     </cfRule>
